--- a/03_BOM/Satellite_4U_PEE_V100.xlsx
+++ b/03_BOM/Satellite_4U_PEE_V100.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Altium_WorkSpace\2_Satellite_1\Satellite_4U_EXP_HW_1.0.0\03_BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BAEB9F69-A3BB-49E6-A4DB-639DA0C83C9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A359198C-1923-4D23-A8F6-14A31AD25A1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{92AD7317-08C2-4C96-BE61-09489C3F9F0C}"/>
+    <workbookView xWindow="-23148" yWindow="2220" windowWidth="23256" windowHeight="12456" xr2:uid="{92AD7317-08C2-4C96-BE61-09489C3F9F0C}"/>
   </bookViews>
   <sheets>
     <sheet name="Satellite_4U_PEE_V100" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="995" uniqueCount="495">
   <si>
     <t>Comment</t>
   </si>
@@ -1518,6 +1518,12 @@
   </si>
   <si>
     <t>USBLC6-2SC6.IntLib</t>
+  </si>
+  <si>
+    <t>RPC2512JT10R0</t>
+  </si>
+  <si>
+    <t>CRM2512-FX-20R0ELF</t>
   </si>
 </sst>
 </file>
@@ -1533,7 +1539,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1543,6 +1549,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD3D3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1574,12 +1586,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1914,10 +1929,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{287328A2-A107-440C-A76C-A611444B9C99}">
-  <dimension ref="A1:K116"/>
+  <dimension ref="A1:K117"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.21875" customWidth="1"/>
+    <col min="1" max="1" width="23.44140625" customWidth="1"/>
     <col min="2" max="2" width="28.109375" customWidth="1"/>
     <col min="3" max="3" width="29.77734375" customWidth="1"/>
     <col min="4" max="4" width="11.77734375" customWidth="1"/>
@@ -3103,69 +3118,53 @@
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
+    <row r="35" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="5"/>
+      <c r="C35" s="5"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
+      <c r="J35" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="K35" s="5"/>
+    </row>
+    <row r="36" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="B36" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C36" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="D36" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E35" s="1">
+      <c r="E36" s="6">
         <v>16</v>
       </c>
-      <c r="F35" s="1">
-        <v>0</v>
-      </c>
-      <c r="G35" s="2" t="s">
+      <c r="F36" s="6">
+        <v>0</v>
+      </c>
+      <c r="G36" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="H35" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
-      <c r="K35" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E36" s="1">
-        <v>133</v>
-      </c>
-      <c r="F36" s="1">
-        <v>0</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I36" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="J36" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="K36" s="2" t="s">
+      <c r="H36" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I36" s="6"/>
+      <c r="J36" s="6" t="s">
+        <v>494</v>
+      </c>
+      <c r="K36" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -3174,16 +3173,16 @@
         <v>137</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E37" s="1">
-        <v>82</v>
+        <v>133</v>
       </c>
       <c r="F37" s="1">
         <v>0</v>
@@ -3195,10 +3194,10 @@
         <v>15</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>141</v>
+        <v>32</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="K37" s="2" t="s">
         <v>14</v>
@@ -3206,34 +3205,34 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="E38" s="1">
-        <v>4</v>
+        <v>82</v>
       </c>
       <c r="F38" s="1">
         <v>0</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>49</v>
+        <v>141</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>14</v>
@@ -3241,34 +3240,34 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="E39" s="1">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F39" s="1">
         <v>0</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="K39" s="2" t="s">
         <v>14</v>
@@ -3276,34 +3275,34 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="E40" s="1">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F40" s="1">
         <v>0</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="K40" s="2" t="s">
         <v>14</v>
@@ -3311,34 +3310,34 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>154</v>
+        <v>45</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>115</v>
+        <v>39</v>
       </c>
       <c r="E41" s="1">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F41" s="1">
         <v>0</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>116</v>
+        <v>40</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>155</v>
+        <v>41</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="K41" s="2" t="s">
         <v>14</v>
@@ -3346,34 +3345,34 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="C42" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E42" s="1">
         <v>29</v>
       </c>
-      <c r="D42" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E42" s="1">
-        <v>6</v>
-      </c>
       <c r="F42" s="1">
         <v>0</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>31</v>
+        <v>116</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>32</v>
+        <v>155</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="K42" s="2" t="s">
         <v>14</v>
@@ -3381,19 +3380,19 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E43" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F43" s="1">
         <v>0</v>
@@ -3408,7 +3407,7 @@
         <v>32</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="K43" s="2" t="s">
         <v>14</v>
@@ -3416,13 +3415,13 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>30</v>
@@ -3440,10 +3439,10 @@
         <v>15</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>165</v>
+        <v>32</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="K44" s="2" t="s">
         <v>14</v>
@@ -3451,10 +3450,10 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>29</v>
@@ -3463,7 +3462,7 @@
         <v>30</v>
       </c>
       <c r="E45" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F45" s="1">
         <v>0</v>
@@ -3475,10 +3474,10 @@
         <v>15</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>32</v>
+        <v>165</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="K45" s="2" t="s">
         <v>14</v>
@@ -3486,10 +3485,10 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>29</v>
@@ -3498,7 +3497,7 @@
         <v>30</v>
       </c>
       <c r="E46" s="1">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F46" s="1">
         <v>0</v>
@@ -3513,7 +3512,7 @@
         <v>32</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K46" s="2" t="s">
         <v>14</v>
@@ -3521,34 +3520,34 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="E47" s="1">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F47" s="1">
         <v>0</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="K47" s="2" t="s">
         <v>14</v>
@@ -3556,34 +3555,34 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="E48" s="1">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="F48" s="1">
         <v>0</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>141</v>
+        <v>41</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="K48" s="2" t="s">
         <v>14</v>
@@ -3591,10 +3590,10 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>35</v>
@@ -3603,7 +3602,7 @@
         <v>30</v>
       </c>
       <c r="E49" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F49" s="1">
         <v>0</v>
@@ -3615,10 +3614,10 @@
         <v>15</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>84</v>
+        <v>141</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="K49" s="2" t="s">
         <v>14</v>
@@ -3626,19 +3625,19 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E50" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F50" s="1">
         <v>0</v>
@@ -3650,10 +3649,10 @@
         <v>15</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>32</v>
+        <v>84</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="K50" s="2" t="s">
         <v>14</v>
@@ -3661,49 +3660,51 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>187</v>
+        <v>29</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>188</v>
+        <v>30</v>
       </c>
       <c r="E51" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F51" s="1">
         <v>0</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>189</v>
+        <v>31</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>190</v>
+        <v>15</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>191</v>
+        <v>32</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="K51" s="1"/>
+        <v>184</v>
+      </c>
+      <c r="K51" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>14</v>
+        <v>188</v>
       </c>
       <c r="E52" s="1">
         <v>1</v>
@@ -3712,40 +3713,40 @@
         <v>0</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>15</v>
+        <v>190</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>191</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="K52" s="1"/>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E53" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F53" s="1">
         <v>0</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>15</v>
@@ -3754,33 +3755,31 @@
         <v>191</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="K53" s="2" t="s">
-        <v>14</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="K53" s="1"/>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E54" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F54" s="1">
         <v>0</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>15</v>
@@ -3789,7 +3788,7 @@
         <v>191</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="K54" s="2" t="s">
         <v>14</v>
@@ -3797,25 +3796,25 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E55" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F55" s="1">
         <v>0</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>15</v>
@@ -3824,7 +3823,7 @@
         <v>191</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="K55" s="2" t="s">
         <v>14</v>
@@ -3832,25 +3831,25 @@
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E56" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F56" s="1">
         <v>0</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>15</v>
@@ -3859,7 +3858,7 @@
         <v>191</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="K56" s="2" t="s">
         <v>14</v>
@@ -3867,13 +3866,13 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>14</v>
@@ -3885,7 +3884,7 @@
         <v>0</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>15</v>
@@ -3894,7 +3893,7 @@
         <v>191</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="K57" s="2" t="s">
         <v>14</v>
@@ -3902,49 +3901,51 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>226</v>
+        <v>14</v>
       </c>
       <c r="E58" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F58" s="1">
         <v>0</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>191</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="K58" s="1"/>
+        <v>222</v>
+      </c>
+      <c r="K58" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>14</v>
+        <v>226</v>
       </c>
       <c r="E59" s="1">
         <v>1</v>
@@ -3953,28 +3954,28 @@
         <v>0</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>196</v>
+        <v>225</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>15</v>
+        <v>227</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>191</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="K59" s="1"/>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>14</v>
@@ -3986,7 +3987,7 @@
         <v>0</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>15</v>
@@ -3995,31 +3996,31 @@
         <v>191</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="K60" s="1"/>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E61" s="1">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F61" s="1">
         <v>0</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>15</v>
@@ -4028,33 +4029,31 @@
         <v>191</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="K61" s="2" t="s">
-        <v>14</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="K61" s="1"/>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E62" s="1">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F62" s="1">
         <v>0</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>15</v>
@@ -4063,75 +4062,75 @@
         <v>191</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="K62" s="1"/>
+        <v>242</v>
+      </c>
+      <c r="K62" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>250</v>
+        <v>14</v>
       </c>
       <c r="E63" s="1">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="F63" s="1">
         <v>0</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>251</v>
+        <v>216</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>252</v>
+        <v>191</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="K63" s="2" t="s">
-        <v>14</v>
-      </c>
+        <v>246</v>
+      </c>
+      <c r="K63" s="1"/>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>14</v>
+        <v>250</v>
       </c>
       <c r="E64" s="1">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="F64" s="1">
         <v>0</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="K64" s="2" t="s">
         <v>14</v>
@@ -4139,49 +4138,51 @@
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E65" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F65" s="1">
         <v>0</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="K65" s="1"/>
+        <v>253</v>
+      </c>
+      <c r="K65" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>265</v>
+        <v>3</v>
       </c>
       <c r="E66" s="1">
         <v>1</v>
@@ -4190,152 +4191,150 @@
         <v>0</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="K66" s="1"/>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="E67" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F67" s="1">
         <v>0</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="K67" s="2" t="s">
-        <v>14</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="K67" s="1"/>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>271</v>
       </c>
       <c r="E68" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F68" s="1">
         <v>0</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="K68" s="1"/>
+        <v>274</v>
+      </c>
+      <c r="K68" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>284</v>
+        <v>271</v>
       </c>
       <c r="E69" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F69" s="1">
         <v>0</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>49</v>
+        <v>279</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="K69" s="2" t="s">
-        <v>14</v>
-      </c>
+        <v>280</v>
+      </c>
+      <c r="K69" s="1"/>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>249</v>
+        <v>283</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>14</v>
+        <v>284</v>
       </c>
       <c r="E70" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F70" s="1">
         <v>0</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>289</v>
+        <v>49</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="K70" s="2" t="s">
         <v>14</v>
@@ -4343,31 +4342,35 @@
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>292</v>
+        <v>249</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E71" s="1">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F71" s="1">
         <v>0</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="I71" s="1"/>
-      <c r="J71" s="1"/>
+        <v>15</v>
+      </c>
+      <c r="I71" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="J71" s="2" t="s">
+        <v>286</v>
+      </c>
       <c r="K71" s="2" t="s">
         <v>14</v>
       </c>
@@ -4377,32 +4380,28 @@
         <v>290</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>29</v>
+        <v>292</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="E72" s="1">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F72" s="1">
         <v>0</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>31</v>
+        <v>293</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I72" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="J72" s="2" t="s">
-        <v>33</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="I72" s="1"/>
+      <c r="J72" s="1"/>
       <c r="K72" s="2" t="s">
         <v>14</v>
       </c>
@@ -4412,16 +4411,16 @@
         <v>290</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E73" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F73" s="1">
         <v>0</v>
@@ -4432,27 +4431,31 @@
       <c r="H73" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I73" s="1"/>
-      <c r="J73" s="1"/>
+      <c r="I73" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J73" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="K73" s="2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E74" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F74" s="1">
         <v>0</v>
@@ -4463,22 +4466,18 @@
       <c r="H74" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I74" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="J74" s="2" t="s">
-        <v>97</v>
-      </c>
+      <c r="I74" s="1"/>
+      <c r="J74" s="1"/>
       <c r="K74" s="2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>29</v>
@@ -4487,7 +4486,7 @@
         <v>30</v>
       </c>
       <c r="E75" s="1">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="F75" s="1">
         <v>0</v>
@@ -4502,7 +4501,7 @@
         <v>32</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="K75" s="2" t="s">
         <v>14</v>
@@ -4513,16 +4512,16 @@
         <v>299</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E76" s="1">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F76" s="1">
         <v>0</v>
@@ -4537,7 +4536,7 @@
         <v>32</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K76" s="2" t="s">
         <v>14</v>
@@ -4545,19 +4544,19 @@
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E77" s="1">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F77" s="1">
         <v>0</v>
@@ -4572,22 +4571,24 @@
         <v>32</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="K77" s="1"/>
+        <v>108</v>
+      </c>
+      <c r="K77" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>306</v>
+        <v>29</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="E78" s="1">
         <v>1</v>
@@ -4596,28 +4597,28 @@
         <v>0</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>307</v>
+        <v>31</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>308</v>
+        <v>32</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>309</v>
+        <v>139</v>
       </c>
       <c r="K78" s="1"/>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>14</v>
@@ -4629,31 +4630,31 @@
         <v>0</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="K79" s="1"/>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>319</v>
+        <v>14</v>
       </c>
       <c r="E80" s="1">
         <v>1</v>
@@ -4662,31 +4663,31 @@
         <v>0</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>321</v>
+        <v>15</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>279</v>
+        <v>314</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="K80" s="1"/>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="E81" s="1">
         <v>1</v>
@@ -4695,59 +4696,61 @@
         <v>0</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>15</v>
+        <v>321</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>327</v>
+        <v>279</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="K81" s="1"/>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>14</v>
+        <v>325</v>
       </c>
       <c r="E82" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F82" s="1">
         <v>0</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I82" s="1"/>
-      <c r="J82" s="1"/>
-      <c r="K82" s="2" t="s">
-        <v>14</v>
-      </c>
+      <c r="I82" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="J82" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="K82" s="1"/>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>14</v>
@@ -4759,66 +4762,64 @@
         <v>0</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I83" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="J83" s="2" t="s">
-        <v>336</v>
-      </c>
+      <c r="I83" s="1"/>
+      <c r="J83" s="1"/>
       <c r="K83" s="2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>340</v>
+        <v>14</v>
       </c>
       <c r="E84" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F84" s="1">
         <v>0</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="K84" s="1"/>
+        <v>336</v>
+      </c>
+      <c r="K84" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>188</v>
+        <v>340</v>
       </c>
       <c r="E85" s="1">
         <v>1</v>
@@ -4827,7 +4828,7 @@
         <v>0</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>15</v>
@@ -4836,75 +4837,73 @@
         <v>342</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="K85" s="1"/>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>64</v>
+        <v>345</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>349</v>
+        <v>188</v>
       </c>
       <c r="E86" s="1">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F86" s="1">
         <v>0</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="K86" s="2" t="s">
-        <v>14</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="K86" s="1"/>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>354</v>
+        <v>64</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="E87" s="1">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F87" s="1">
         <v>0</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="K87" s="2" t="s">
         <v>14</v>
@@ -4912,34 +4911,34 @@
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="E88" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F88" s="1">
         <v>0</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="K88" s="2" t="s">
         <v>14</v>
@@ -4947,81 +4946,81 @@
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="E89" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F89" s="1">
         <v>0</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="K89" s="1"/>
+        <v>358</v>
+      </c>
+      <c r="K89" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>14</v>
+        <v>366</v>
       </c>
       <c r="E90" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F90" s="1">
         <v>0</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>76</v>
+        <v>15</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="K90" s="2" t="s">
-        <v>14</v>
-      </c>
+        <v>363</v>
+      </c>
+      <c r="K90" s="1"/>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>14</v>
@@ -5033,62 +5032,64 @@
         <v>0</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="I91" s="1"/>
-      <c r="J91" s="1"/>
+        <v>76</v>
+      </c>
+      <c r="I91" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="J91" s="2" t="s">
+        <v>368</v>
+      </c>
       <c r="K91" s="2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>381</v>
+        <v>14</v>
       </c>
       <c r="E92" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F92" s="1">
         <v>0</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I92" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="J92" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="K92" s="1"/>
+        <v>377</v>
+      </c>
+      <c r="I92" s="1"/>
+      <c r="J92" s="1"/>
+      <c r="K92" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="E93" s="1">
         <v>1</v>
@@ -5097,7 +5098,7 @@
         <v>0</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="H93" s="2" t="s">
         <v>15</v>
@@ -5106,22 +5107,22 @@
         <v>372</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="K93" s="1"/>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>14</v>
+        <v>385</v>
       </c>
       <c r="E94" s="1">
         <v>1</v>
@@ -5130,31 +5131,31 @@
         <v>0</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>308</v>
+        <v>372</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="K94" s="1"/>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>395</v>
+        <v>14</v>
       </c>
       <c r="E95" s="1">
         <v>1</v>
@@ -5163,31 +5164,31 @@
         <v>0</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="K95" s="1"/>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>14</v>
+        <v>395</v>
       </c>
       <c r="E96" s="1">
         <v>1</v>
@@ -5196,26 +5197,28 @@
         <v>0</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I96" s="1"/>
-      <c r="J96" s="1"/>
-      <c r="K96" s="2" t="s">
-        <v>14</v>
-      </c>
+      <c r="I96" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="J96" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="K96" s="1"/>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>14</v>
@@ -5227,24 +5230,26 @@
         <v>0</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
       <c r="I97" s="1"/>
       <c r="J97" s="1"/>
-      <c r="K97" s="1"/>
+      <c r="K97" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>14</v>
@@ -5256,167 +5261,163 @@
         <v>0</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="I98" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="J98" s="2" t="s">
-        <v>405</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="I98" s="1"/>
+      <c r="J98" s="1"/>
       <c r="K98" s="1"/>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>394</v>
+        <v>407</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E99" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F99" s="1">
         <v>0</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>76</v>
+        <v>408</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>362</v>
+        <v>409</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="K99" s="2" t="s">
-        <v>14</v>
-      </c>
+        <v>405</v>
+      </c>
+      <c r="K99" s="1"/>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>414</v>
+        <v>394</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E100" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F100" s="1">
         <v>0</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>15</v>
+        <v>76</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>314</v>
+        <v>362</v>
       </c>
       <c r="J100" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="K100" s="1"/>
+        <v>410</v>
+      </c>
+      <c r="K100" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E101" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F101" s="1">
         <v>0</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>76</v>
+        <v>15</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>420</v>
+        <v>314</v>
       </c>
       <c r="J101" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="K101" s="2" t="s">
-        <v>14</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="K101" s="1"/>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>424</v>
+        <v>14</v>
       </c>
       <c r="E102" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F102" s="1">
         <v>0</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>426</v>
+        <v>76</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="J102" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="K102" s="1"/>
+        <v>417</v>
+      </c>
+      <c r="K102" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="E103" s="1">
         <v>1</v>
@@ -5425,31 +5426,31 @@
         <v>0</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>15</v>
+        <v>426</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>314</v>
+        <v>427</v>
       </c>
       <c r="J103" s="2" t="s">
-        <v>432</v>
+        <v>421</v>
       </c>
       <c r="K103" s="1"/>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="E104" s="1">
         <v>1</v>
@@ -5458,152 +5459,150 @@
         <v>0</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>437</v>
+        <v>428</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>321</v>
+        <v>15</v>
       </c>
       <c r="I104" s="2" t="s">
         <v>314</v>
       </c>
       <c r="J104" s="2" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="K104" s="1"/>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="E105" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F105" s="1">
         <v>0</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>443</v>
+        <v>321</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>362</v>
+        <v>314</v>
       </c>
       <c r="J105" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="K105" s="2" t="s">
-        <v>14</v>
-      </c>
+        <v>438</v>
+      </c>
+      <c r="K105" s="1"/>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="E106" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F106" s="1">
         <v>0</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>15</v>
+        <v>443</v>
       </c>
       <c r="I106" s="2" t="s">
         <v>362</v>
       </c>
       <c r="J106" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="K106" s="1"/>
+        <v>439</v>
+      </c>
+      <c r="K106" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="E107" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F107" s="1">
         <v>0</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>77</v>
+        <v>362</v>
       </c>
       <c r="J107" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="K107" s="2" t="s">
-        <v>14</v>
-      </c>
+        <v>444</v>
+      </c>
+      <c r="K107" s="1"/>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="E108" s="1">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F108" s="1">
         <v>0</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>457</v>
+        <v>77</v>
       </c>
       <c r="J108" s="2" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="K108" s="2" t="s">
         <v>14</v>
@@ -5611,34 +5610,34 @@
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="E109" s="1">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F109" s="1">
         <v>0</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="J109" s="2" t="s">
-        <v>464</v>
+        <v>453</v>
       </c>
       <c r="K109" s="2" t="s">
         <v>14</v>
@@ -5646,49 +5645,51 @@
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>249</v>
+        <v>460</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="E110" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F110" s="1">
         <v>0</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I110" s="2" t="s">
-        <v>314</v>
+        <v>463</v>
       </c>
       <c r="J110" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="K110" s="1"/>
+        <v>464</v>
+      </c>
+      <c r="K110" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>471</v>
+        <v>249</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>14</v>
+        <v>467</v>
       </c>
       <c r="E111" s="1">
         <v>1</v>
@@ -5697,28 +5698,28 @@
         <v>0</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>473</v>
+        <v>15</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>362</v>
+        <v>314</v>
       </c>
       <c r="J111" s="2" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="K111" s="1"/>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>333</v>
+        <v>471</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>14</v>
@@ -5730,154 +5731,187 @@
         <v>0</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="I112" s="2" t="s">
         <v>362</v>
       </c>
       <c r="J112" s="2" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="K112" s="1"/>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>479</v>
+        <v>333</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>480</v>
+        <v>14</v>
       </c>
       <c r="E113" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F113" s="1">
         <v>0</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>76</v>
+        <v>476</v>
       </c>
       <c r="I113" s="2" t="s">
         <v>362</v>
       </c>
       <c r="J113" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="K113" s="2" t="s">
-        <v>14</v>
-      </c>
+        <v>474</v>
+      </c>
+      <c r="K113" s="1"/>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="E114" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F114" s="1">
         <v>0</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>15</v>
+        <v>76</v>
       </c>
       <c r="I114" s="2" t="s">
         <v>362</v>
       </c>
       <c r="J114" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="K114" s="1"/>
+        <v>477</v>
+      </c>
+      <c r="K114" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>14</v>
+        <v>484</v>
       </c>
       <c r="E115" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F115" s="1">
         <v>0</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>76</v>
+        <v>15</v>
       </c>
       <c r="I115" s="2" t="s">
         <v>362</v>
       </c>
       <c r="J115" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="K115" s="2" t="s">
-        <v>14</v>
-      </c>
+        <v>481</v>
+      </c>
+      <c r="K115" s="1"/>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E116" s="1">
+        <v>7</v>
+      </c>
+      <c r="F116" s="1">
+        <v>0</v>
+      </c>
+      <c r="G116" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I116" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="J116" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="K116" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A117" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="B116" s="2" t="s">
+      <c r="B117" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="C116" s="2" t="s">
+      <c r="C117" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="D116" s="2" t="s">
+      <c r="D117" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="E116" s="1">
+      <c r="E117" s="1">
         <v>2</v>
       </c>
-      <c r="F116" s="1">
-        <v>0</v>
-      </c>
-      <c r="G116" s="2" t="s">
+      <c r="F117" s="1">
+        <v>0</v>
+      </c>
+      <c r="G117" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="H116" s="2" t="s">
+      <c r="H117" s="2" t="s">
         <v>492</v>
       </c>
-      <c r="I116" s="2" t="s">
+      <c r="I117" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="J116" s="2" t="s">
+      <c r="J117" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="K116" s="2" t="s">
+      <c r="K117" s="2" t="s">
         <v>14</v>
       </c>
     </row>

--- a/03_BOM/Satellite_4U_PEE_V100.xlsx
+++ b/03_BOM/Satellite_4U_PEE_V100.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Altium_WorkSpace\2_Satellite_1\Satellite_4U_EXP_HW_1.0.0\03_BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A359198C-1923-4D23-A8F6-14A31AD25A1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D866B64-CE52-4C25-9230-D450BFD5C256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="2220" windowWidth="23256" windowHeight="12456" xr2:uid="{92AD7317-08C2-4C96-BE61-09489C3F9F0C}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="30912" windowHeight="16752" xr2:uid="{92AD7317-08C2-4C96-BE61-09489C3F9F0C}"/>
   </bookViews>
   <sheets>
     <sheet name="Satellite_4U_PEE_V100" sheetId="1" r:id="rId1"/>
@@ -1539,7 +1539,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1555,6 +1555,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1586,7 +1592,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
@@ -1595,6 +1601,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2174,7 +2181,7 @@
       <c r="I7" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="J7" s="8" t="s">
         <v>33</v>
       </c>
       <c r="K7" s="2" t="s">
